--- a/rapport/empty-queue-data.xlsx
+++ b/rapport/empty-queue-data.xlsx
@@ -5,64 +5,18 @@
   <workbookPr dateCompatibility="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/baptistedupertuis/Documents/Etudes/MSE/PCM/Projet/v2/PCM_FinalProject/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/baptistedupertuis/Documents/Etudes/MSE/PCM/Projet/v2/PCM_FinalProject/rapport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{14CFD34B-CFB6-DD43-A229-8756AE296E84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{316710C3-481A-AF44-B6E5-F2FBBC46F5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="-1920" windowWidth="38400" windowHeight="21100" xr2:uid="{484D20E6-2301-4D49-A5A3-FE8C8485E710}"/>
+    <workbookView xWindow="35100" yWindow="-1920" windowWidth="34560" windowHeight="21100" xr2:uid="{484D20E6-2301-4D49-A5A3-FE8C8485E710}"/>
   </bookViews>
   <sheets>
     <sheet name="empty-queue-data" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil1" sheetId="2" r:id="rId2"/>
+    <sheet name="Feuil2" sheetId="3" r:id="rId2"/>
+    <sheet name="Feuil1" sheetId="2" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'empty-queue-data'!$A$77:$A$84</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'empty-queue-data'!$B$76</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">'empty-queue-data'!$B$76</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">'empty-queue-data'!$B$77:$B$84</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">'empty-queue-data'!$C$76</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">'empty-queue-data'!$C$77:$C$84</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">'empty-queue-data'!$D$76</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">'empty-queue-data'!$D$77:$D$84</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">'empty-queue-data'!$E$76</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">'empty-queue-data'!$E$77:$E$84</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">'empty-queue-data'!$A$77:$A$84</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">'empty-queue-data'!$B$76</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'empty-queue-data'!$B$77:$B$84</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">'empty-queue-data'!$B$77:$B$84</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">'empty-queue-data'!$C$76</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">'empty-queue-data'!$C$77:$C$84</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">'empty-queue-data'!$D$76</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">'empty-queue-data'!$D$77:$D$84</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">'empty-queue-data'!$E$76</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">'empty-queue-data'!$E$77:$E$84</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">'empty-queue-data'!$A$77:$A$84</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">'empty-queue-data'!$B$76</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">'empty-queue-data'!$B$77:$B$84</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'empty-queue-data'!$C$76</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">'empty-queue-data'!$C$76</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">'empty-queue-data'!$C$77:$C$84</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">'empty-queue-data'!$D$76</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">'empty-queue-data'!$D$77:$D$84</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">'empty-queue-data'!$E$76</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">'empty-queue-data'!$E$77:$E$84</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">'empty-queue-data'!$A$77:$A$84</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">'empty-queue-data'!$B$76</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">'empty-queue-data'!$B$77:$B$84</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">'empty-queue-data'!$C$76</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'empty-queue-data'!$C$77:$C$84</definedName>
-    <definedName name="_xlchart.v1.40" hidden="1">'empty-queue-data'!$C$77:$C$84</definedName>
-    <definedName name="_xlchart.v1.41" hidden="1">'empty-queue-data'!$D$76</definedName>
-    <definedName name="_xlchart.v1.42" hidden="1">'empty-queue-data'!$D$77:$D$84</definedName>
-    <definedName name="_xlchart.v1.43" hidden="1">'empty-queue-data'!$E$76</definedName>
-    <definedName name="_xlchart.v1.44" hidden="1">'empty-queue-data'!$E$77:$E$84</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'empty-queue-data'!$D$76</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">'empty-queue-data'!$D$77:$D$84</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">'empty-queue-data'!$E$76</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">'empty-queue-data'!$E$77:$E$84</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">'empty-queue-data'!$A$77:$A$84</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -84,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="60" uniqueCount="23">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="72" uniqueCount="28">
   <si>
     <t>Cities</t>
   </si>
@@ -154,12 +108,27 @@
   <si>
     <t>efficience</t>
   </si>
+  <si>
+    <t>Standard_deviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">max_depth </t>
+  </si>
+  <si>
+    <t>final job size @ 10</t>
+  </si>
+  <si>
+    <t>final job size @ 12</t>
+  </si>
+  <si>
+    <t>final job size @ 14</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -300,6 +269,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -483,7 +458,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <start/>
       <end/>
@@ -598,6 +573,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <start/>
+      <end style="thin">
+        <color indexed="64"/>
+      </end>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -643,9 +627,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1320,7 +1306,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -1333,7 +1319,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR"/>
+                  <a:rPr lang="fr-FR" sz="1200"/>
                   <a:t>Nb Threads</a:t>
                 </a:r>
               </a:p>
@@ -1352,7 +1338,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -1439,6 +1425,596 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65%"/>
+                        <a:lumOff val="35%"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-FR" sz="1200"/>
+                  <a:t>Temps [ms]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65%"/>
+                      <a:lumOff val="35%"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25%"/>
+                <a:lumOff val="75%"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65%"/>
+                    <a:lumOff val="35%"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1258330768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65%"/>
+                  <a:lumOff val="35%"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15%"/>
+          <a:lumOff val="85%"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://purl.oclc.org/ooxml/drawingml/chart" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0%">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65%"/>
+                    <a:lumOff val="35%"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-FR"/>
+              <a:t>Final Job size affect (17</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="fr-FR" baseline="0%"/>
+              <a:t> villes) - Variance du temps d'exécution </a:t>
+            </a:r>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0%">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65%"/>
+                  <a:lumOff val="35%"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil2!$C$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>final job size @ 10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Feuil2!$B$25:$B$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>256</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Feuil2!$C$25:$C$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1.8708</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.3811</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.6226000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45.640500000000003</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14.946099999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21.526299999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25.939</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30.686699999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1BAC-1549-810F-B44DA8A32D7F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil2!$D$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>final job size @ 12</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Feuil2!$B$25:$B$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>256</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Feuil2!$D$25:$D$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>2.5644</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.2820999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.6848000000000001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.569000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16.438300000000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18.258600000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18.699100000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.902999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1BAC-1549-810F-B44DA8A32D7F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil2!$E$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>final job size @ 14</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Feuil2!$B$25:$B$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>256</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Feuil2!$E$25:$E$32</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>5638.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6035.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6483.35</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5022</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4718.16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4502.5249999999996</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4364.9049999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4211.7749999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1BAC-1549-810F-B44DA8A32D7F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="248609776"/>
+        <c:axId val="395380336"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="248609776"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="256"/>
+          <c:min val="32"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15%"/>
+                  <a:lumOff val="85%"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
@@ -1453,7 +2029,144 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="fr-FR"/>
-                  <a:t>Temps [ms]</a:t>
+                  <a:t>Nombres</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="fr-FR" baseline="0%"/>
+                  <a:t> de threads</a:t>
+                </a:r>
+                <a:endParaRPr lang="fr-FR"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.43232898213304738"/>
+              <c:y val="0.84101537307836527"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65%"/>
+                      <a:lumOff val="35%"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25%"/>
+                <a:lumOff val="75%"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65%"/>
+                    <a:lumOff val="35%"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="395380336"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="395380336"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15%"/>
+                  <a:lumOff val="85%"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65%"/>
+                        <a:lumOff val="35%"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-FR" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65%"/>
+                        <a:lumOff val="35%"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Variance du temps d'exécution [ms]</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1524,7 +2237,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1258330768"/>
+        <c:crossAx val="248609776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1611,7 +2324,899 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://purl.oclc.org/ooxml/drawingml/chart" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0%">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65%"/>
+                    <a:lumOff val="35%"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="fr-FR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0%">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65%"/>
+                    <a:lumOff val="35%"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Temps d'exécussion V2 </a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0%">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65%"/>
+                  <a:lumOff val="35%"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$B$76</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>18 villes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Feuil1!$A$77:$A$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>256</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Feuil1!$B$77:$B$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>227622.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>138852.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>114043.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>91447</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>85845.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>82812.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>93098.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>87560</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0AB2-1842-BBA4-D50556DC3F56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$C$76</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>17 villes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Feuil1!$A$77:$A$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>256</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Feuil1!$C$77:$C$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>49581.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>26587.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>22472.1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16816.099999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18198.900000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20725.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19718.900000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19737</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0AB2-1842-BBA4-D50556DC3F56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$D$76</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>16 villes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Feuil1!$A$77:$A$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>256</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Feuil1!$D$77:$D$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>9728.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6550.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6308.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6090.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7188.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7305.3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8069.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8456.7999999999993</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0AB2-1842-BBA4-D50556DC3F56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$E$76</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>15 villes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Feuil1!$A$77:$A$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>256</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Feuil1!$E$77:$E$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>3725.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3213.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3936.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4229.1000000000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4490.8999999999996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6050.7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6476.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7488.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0AB2-1842-BBA4-D50556DC3F56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$F$76</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>14 villes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Feuil1!$A$77:$A$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>96</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>224</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>256</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Feuil1!$F$77:$F$84</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>884.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>743.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>760</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>846.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>888.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>988.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1012.1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1078.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-0AB2-1842-BBA4-D50556DC3F56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1463334015"/>
+        <c:axId val="510930208"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1463334015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="256"/>
+          <c:min val="32"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15%"/>
+                  <a:lumOff val="85%"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65%"/>
+                        <a:lumOff val="35%"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-FR" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65%"/>
+                        <a:lumOff val="35%"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Nb Threads</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65%"/>
+                      <a:lumOff val="35%"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25%"/>
+                <a:lumOff val="75%"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65%"/>
+                    <a:lumOff val="35%"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="510930208"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="510930208"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="230000"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15%"/>
+                  <a:lumOff val="85%"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65%"/>
+                        <a:lumOff val="35%"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="fr-FR" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65%"/>
+                        <a:lumOff val="35%"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Temps [ms]</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65%"/>
+                      <a:lumOff val="35%"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="fr-FR"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25%"/>
+                <a:lumOff val="75%"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65%"/>
+                    <a:lumOff val="35%"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1463334015"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15%"/>
+          <a:lumOff val="85%"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://purl.oclc.org/ooxml/drawingml/chart" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -1952,7 +3557,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://purl.oclc.org/ooxml/drawingml/chart" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -2384,7 +3989,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://purl.oclc.org/ooxml/drawingml/chart" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -2525,28 +4130,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>21.966184377122481</c:v>
+                  <c:v>28.739666535748206</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>36.009330737780772</c:v>
+                  <c:v>47.113150823641426</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43.84276581211271</c:v>
+                  <c:v>57.362100208779253</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>54.676479272146707</c:v>
+                  <c:v>71.536492394501735</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>58.24423906231435</c:v>
+                  <c:v>76.204404895311811</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>60.377577216883502</c:v>
+                  <c:v>78.995578187754944</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>53.706731172031255</c:v>
+                  <c:v>70.267713231834776</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>57.103700319780721</c:v>
+                  <c:v>74.712170169026948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2624,28 +4229,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>9.6810497484943951</c:v>
+                  <c:v>22.948964268858887</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.053664517779097</c:v>
+                  <c:v>42.796278575565864</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21.359819509525146</c:v>
+                  <c:v>50.633531223161171</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28.544073834004319</c:v>
+                  <c:v>67.663832696047251</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>26.375220480358699</c:v>
+                  <c:v>62.522557791954455</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>23.159652026228304</c:v>
+                  <c:v>54.900040867135971</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>24.342128617722082</c:v>
+                  <c:v>57.703106004898849</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>24.319805441556468</c:v>
+                  <c:v>57.650188833156001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2723,28 +4328,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>49.337540729167742</c:v>
+                  <c:v>23.456902681700914</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>73.277967757694185</c:v>
+                  <c:v>34.839072499389353</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>76.08661192657641</c:v>
+                  <c:v>36.174406445170085</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>78.806087770280257</c:v>
+                  <c:v>37.467346451263367</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>66.772389616893406</c:v>
+                  <c:v>31.746078582756031</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>65.705720504291406</c:v>
+                  <c:v>31.238944396534023</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>59.481028030434459</c:v>
+                  <c:v>28.279493977545911</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>56.75905779964053</c:v>
+                  <c:v>26.985368047015424</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2822,28 +4427,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.26839152956332696</c:v>
+                  <c:v>12.451431332027161</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.31121623303871532</c:v>
+                  <c:v>14.438188721523716</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.25401341190814875</c:v>
+                  <c:v>11.784390367811421</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.23645692937031518</c:v>
+                  <c:v>10.969896195408005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.22267251553140799</c:v>
+                  <c:v>10.330398806475317</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1652701340340787</c:v>
+                  <c:v>7.6673422909745979</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.15440438508453641</c:v>
+                  <c:v>7.1632499034972597</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.13353809174066902</c:v>
+                  <c:v>6.1952043800494092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3220,7 +4825,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://purl.oclc.org/ooxml/drawingml/chart" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="fr-FR"/>
@@ -3361,28 +4966,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.68644326178507753</c:v>
+                  <c:v>0.89811457924213145</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.56264579277782456</c:v>
+                  <c:v>0.73614298161939729</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.45669547720950737</c:v>
+                  <c:v>0.59752187717478389</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.42715999431364615</c:v>
+                  <c:v>0.55887884683204481</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3640264941394647</c:v>
+                  <c:v>0.47627753059569883</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.31446654800460155</c:v>
+                  <c:v>0.41143530306122367</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.23976219273228239</c:v>
+                  <c:v>0.31369514835640527</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.22306132937414344</c:v>
+                  <c:v>0.29184441472276151</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3460,28 +5065,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.30253280464044985</c:v>
+                  <c:v>0.71715513340184023</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2820885080902984</c:v>
+                  <c:v>0.66869185274321663</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.22249811989088694</c:v>
+                  <c:v>0.52743261690792886</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22300057682815874</c:v>
+                  <c:v>0.52862369293786915</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.16484512800224188</c:v>
+                  <c:v>0.39076598619971536</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.12062318763660575</c:v>
+                  <c:v>0.28593771284966651</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.10867021704340216</c:v>
+                  <c:v>0.25760315180758414</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.4999240006079955E-2</c:v>
+                  <c:v>0.22519605012951563</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3559,28 +5164,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>1.5417981477864919</c:v>
+                  <c:v>0.73302820880315356</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.1449682462139716</c:v>
+                  <c:v>0.54436050780295864</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.79256887423517097</c:v>
+                  <c:v>0.37681673380385505</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.61567256070531451</c:v>
+                  <c:v>0.29271364415049506</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.41732743510558379</c:v>
+                  <c:v>0.19841299114222519</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.34221729429318443</c:v>
+                  <c:v>0.16270283539861471</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2655403037072967</c:v>
+                  <c:v>0.1262477409711871</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.22171506952984582</c:v>
+                  <c:v>0.105411593933654</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3658,28 +5263,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>8.3872352988539674E-3</c:v>
+                  <c:v>0.38910722912584877</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.8627536412299268E-3</c:v>
+                  <c:v>0.22559669877380806</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.6459730407098828E-3</c:v>
+                  <c:v>0.12275406633136897</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8473197607055873E-3</c:v>
+                  <c:v>8.5702314026625037E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3917032220712999E-3</c:v>
+                  <c:v>6.4564992540470739E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.6078194809415985E-4</c:v>
+                  <c:v>3.9934074432159364E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.8930529055596609E-4</c:v>
+                  <c:v>3.1978794212041341E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.2163317086198837E-4</c:v>
+                  <c:v>2.4200017109568005E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4438,8 +6043,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.22356766723332774"/>
-          <c:y val="2.0325205432427215E-2"/>
+          <c:x val="0.3457673412146568"/>
+          <c:y val="2.6309292087728895E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -6015,7 +7620,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -6028,7 +7633,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:rPr lang="fr-FR" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000">
                         <a:lumMod val="65%"/>
@@ -6054,7 +7659,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -6141,7 +7746,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -6154,7 +7759,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:rPr lang="fr-FR" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000">
                         <a:lumMod val="65%"/>
@@ -6180,7 +7785,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -6260,7 +7865,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65%"/>
@@ -6391,7 +7996,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.12254220949321959"/>
+          <c:y val="0.1403390592003966"/>
+          <c:w val="0.835528574281176"/>
+          <c:h val="0.6316084426944546"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -6461,28 +8076,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>22.853225161400903</c:v>
+                  <c:v>29.90023479403531</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44.972643141177223</c:v>
+                  <c:v>58.840385973212499</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46.442547317989337</c:v>
+                  <c:v>60.763549102312005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>64.046400336115511</c:v>
+                  <c:v>83.795717857673537</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>63.660288330177913</c:v>
+                  <c:v>83.290544537374331</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>63.575377510591657</c:v>
+                  <c:v>83.179450657878007</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>67.13707376350294</c:v>
+                  <c:v>87.8394298719696</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>64.69560716827327</c:v>
+                  <c:v>84.645113799573011</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6560,28 +8175,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>11.116489227427158</c:v>
+                  <c:v>26.351678867785573</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22.622301819210104</c:v>
+                  <c:v>53.626250212084081</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>26.604294376517274</c:v>
+                  <c:v>63.065578310849006</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>31.264858949891547</c:v>
+                  <c:v>74.113463885831152</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28.951765152931667</c:v>
+                  <c:v>68.630266476871768</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>29.834418974690468</c:v>
+                  <c:v>70.722600629009008</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>29.389434498297863</c:v>
+                  <c:v>69.667763280350712</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>30.766666880324077</c:v>
+                  <c:v>72.932497740572899</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6659,28 +8274,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>52.34973988722993</c:v>
+                  <c:v>24.889014243491729</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>82.592012664108609</c:v>
+                  <c:v>39.267316017688458</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>96.148068024758118</c:v>
+                  <c:v>45.712369148488676</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>102.18418699706221</c:v>
+                  <c:v>48.582164708136425</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>104.90656758824173</c:v>
+                  <c:v>49.876485739263472</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>110.57105341964018</c:v>
+                  <c:v>52.569593075487781</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>114.19870574800153</c:v>
+                  <c:v>54.294313975066622</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>115.01413715435856</c:v>
+                  <c:v>54.682000407341739</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6758,28 +8373,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.2971150132216181</c:v>
+                  <c:v>13.783993820007726</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.34522042324023894</c:v>
+                  <c:v>16.015737908654678</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.35799949880070164</c:v>
+                  <c:v>16.608594851967208</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.35944071025484348</c:v>
+                  <c:v>16.675456669422381</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.36016567621105711</c:v>
+                  <c:v>16.709089861336214</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3582046781530967</c:v>
+                  <c:v>16.618113694164848</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.35573263135427413</c:v>
+                  <c:v>16.503428551100992</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.35778175313059035</c:v>
+                  <c:v>16.598493023255813</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6832,7 +8447,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -6845,11 +8460,11 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR"/>
+                  <a:rPr lang="fr-FR" sz="1200"/>
                   <a:t>Nombres</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="fr-FR" baseline="0%"/>
+                  <a:rPr lang="fr-FR" sz="1200" baseline="0%"/>
                   <a:t> de threads</a:t>
                 </a:r>
               </a:p>
@@ -6868,7 +8483,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -6953,7 +8568,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -6966,7 +8581,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR"/>
+                  <a:rPr lang="fr-FR" sz="1200"/>
                   <a:t>Speedup</a:t>
                 </a:r>
               </a:p>
@@ -6985,7 +8600,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -7065,7 +8680,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65%"/>
@@ -7196,7 +8811,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11745430480949545"/>
+          <c:y val="0.14025627931974471"/>
+          <c:w val="0.84057011116393276"/>
+          <c:h val="0.62804422880231769"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -7266,28 +8891,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.71416328629377823</c:v>
+                  <c:v>0.93438233731360343</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7026975490808941</c:v>
+                  <c:v>0.91938103083144529</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.48377653456238895</c:v>
+                  <c:v>0.63295363648241676</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.50036250262590243</c:v>
+                  <c:v>0.65465404576307451</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.39787680206361198</c:v>
+                  <c:v>0.52056590335858954</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.3311217578676649</c:v>
+                  <c:v>0.43322630550978131</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.29971907930135239</c:v>
+                  <c:v>0.39214031192843574</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.25271721550106746</c:v>
+                  <c:v>0.33064497577958207</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7365,28 +8990,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.34739028835709868</c:v>
+                  <c:v>0.82348996461829915</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.35347346592515788</c:v>
+                  <c:v>0.83791015956381376</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.27712806642205495</c:v>
+                  <c:v>0.65693310740467714</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.24425671054602771</c:v>
+                  <c:v>0.57901143660805587</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.18094853220582291</c:v>
+                  <c:v>0.42893916548044853</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.15538759882651285</c:v>
+                  <c:v>0.36834687827608859</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.13120283258168688</c:v>
+                  <c:v>0.31101680035870855</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.12018229250126593</c:v>
+                  <c:v>0.28489256929911289</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7464,28 +9089,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>1.6359293714759353</c:v>
+                  <c:v>0.77778169510911654</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.290500197876697</c:v>
+                  <c:v>0.61355181277638215</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0015423752578971</c:v>
+                  <c:v>0.47617051196342369</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.79831396091454854</c:v>
+                  <c:v>0.37954816178231582</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.6556660474265108</c:v>
+                  <c:v>0.31172803587039671</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.57589090322729264</c:v>
+                  <c:v>0.27379996393483219</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.5098156506607211</c:v>
+                  <c:v>0.24238533024583314</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.44927397325921314</c:v>
+                  <c:v>0.21360156409117867</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7563,28 +9188,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>9.2848441631755655E-3</c:v>
+                  <c:v>0.43074980687524145</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.3940691131287334E-3</c:v>
+                  <c:v>0.25024590482272935</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.7291614458406421E-3</c:v>
+                  <c:v>0.17300619637465842</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.8081305488659647E-3</c:v>
+                  <c:v>0.13027700522986235</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.2510354763191067E-3</c:v>
+                  <c:v>0.10443181163335133</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.8656493653807121E-3</c:v>
+                  <c:v>8.6552675490441919E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.5880921042601523E-3</c:v>
+                  <c:v>7.3676020317415145E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3975849731663686E-3</c:v>
+                  <c:v>6.4837863372093019E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7637,7 +9262,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -7650,11 +9275,11 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR"/>
+                  <a:rPr lang="fr-FR" sz="1200"/>
                   <a:t>Nombres</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="fr-FR" baseline="0%"/>
+                  <a:rPr lang="fr-FR" sz="1200" baseline="0%"/>
                   <a:t> de threads</a:t>
                 </a:r>
               </a:p>
@@ -7673,7 +9298,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -7758,7 +9383,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -7771,8 +9396,15 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR"/>
-                  <a:t>Speedup</a:t>
+                  <a:rPr lang="fr-FR" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65%"/>
+                        <a:lumOff val="35%"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Efficience</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -7790,7 +9422,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -7870,7 +9502,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65%"/>
@@ -8001,7 +9633,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.1101994918008062"/>
+          <c:y val="0.13990356742320559"/>
+          <c:w val="0.84848073681405833"/>
+          <c:h val="0.62897961099072386"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -8071,28 +9713,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>21.966184377122481</c:v>
+                  <c:v>28.739666535748206</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>36.009330737780772</c:v>
+                  <c:v>47.113150823641426</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43.84276581211271</c:v>
+                  <c:v>57.362100208779253</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>54.676479272146707</c:v>
+                  <c:v>71.536492394501735</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>58.24423906231435</c:v>
+                  <c:v>76.204404895311811</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>60.377577216883502</c:v>
+                  <c:v>78.995578187754944</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>53.706731172031255</c:v>
+                  <c:v>70.267713231834776</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>57.103700319780721</c:v>
+                  <c:v>74.712170169026948</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8170,28 +9812,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>9.6810497484943951</c:v>
+                  <c:v>22.948964268858887</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>18.053664517779097</c:v>
+                  <c:v>42.796278575565864</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>21.359819509525146</c:v>
+                  <c:v>50.633531223161171</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28.544073834004319</c:v>
+                  <c:v>67.663832696047251</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>26.375220480358699</c:v>
+                  <c:v>62.522557791954455</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>23.159652026228304</c:v>
+                  <c:v>54.900040867135971</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>24.342128617722082</c:v>
+                  <c:v>57.703106004898849</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>24.319805441556468</c:v>
+                  <c:v>57.650188833156001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8269,28 +9911,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>49.337540729167742</c:v>
+                  <c:v>23.456902681700914</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>73.277967757694185</c:v>
+                  <c:v>34.839072499389353</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>76.08661192657641</c:v>
+                  <c:v>36.174406445170085</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>78.806087770280257</c:v>
+                  <c:v>37.467346451263367</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>66.772389616893406</c:v>
+                  <c:v>31.746078582756031</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>65.705720504291406</c:v>
+                  <c:v>31.238944396534023</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>59.481028030434459</c:v>
+                  <c:v>28.279493977545911</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>56.75905779964053</c:v>
+                  <c:v>26.985368047015424</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8368,28 +10010,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.26839152956332696</c:v>
+                  <c:v>12.451431332027161</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.31121623303871532</c:v>
+                  <c:v>14.438188721523716</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.25401341190814875</c:v>
+                  <c:v>11.784390367811421</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.23645692937031518</c:v>
+                  <c:v>10.969896195408005</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.22267251553140799</c:v>
+                  <c:v>10.330398806475317</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1652701340340787</c:v>
+                  <c:v>7.6673422909745979</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.15440438508453641</c:v>
+                  <c:v>7.1632499034972597</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.13353809174066902</c:v>
+                  <c:v>6.1952043800494092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8442,7 +10084,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -8455,7 +10097,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR"/>
+                  <a:rPr lang="fr-FR" sz="1200"/>
                   <a:t>Nombres de threads</a:t>
                 </a:r>
               </a:p>
@@ -8474,7 +10116,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -8573,7 +10215,7 @@
                   <a:buFontTx/>
                   <a:buNone/>
                   <a:tabLst/>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000">
                         <a:lumMod val="65%"/>
@@ -8586,7 +10228,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:rPr lang="fr-FR" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000">
                         <a:lumMod val="65%"/>
@@ -8626,7 +10268,7 @@
                 <a:buFontTx/>
                 <a:buNone/>
                 <a:tabLst/>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumMod val="65%"/>
@@ -8706,7 +10348,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65%"/>
@@ -8837,7 +10479,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11581681092319612"/>
+          <c:y val="0.14014261109750803"/>
+          <c:w val="0.8427928093331134"/>
+          <c:h val="0.61701033182205356"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -8907,28 +10559,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.68644326178507753</c:v>
+                  <c:v>0.89811457924213145</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.56264579277782456</c:v>
+                  <c:v>0.73614298161939729</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.45669547720950737</c:v>
+                  <c:v>0.59752187717478389</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.42715999431364615</c:v>
+                  <c:v>0.55887884683204481</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3640264941394647</c:v>
+                  <c:v>0.47627753059569883</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.31446654800460155</c:v>
+                  <c:v>0.41143530306122367</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.23976219273228239</c:v>
+                  <c:v>0.31369514835640527</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.22306132937414344</c:v>
+                  <c:v>0.29184441472276151</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9006,28 +10658,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0.30253280464044985</c:v>
+                  <c:v>0.71715513340184023</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.2820885080902984</c:v>
+                  <c:v>0.66869185274321663</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.22249811989088694</c:v>
+                  <c:v>0.52743261690792886</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.22300057682815874</c:v>
+                  <c:v>0.52862369293786915</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.16484512800224188</c:v>
+                  <c:v>0.39076598619971536</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.12062318763660575</c:v>
+                  <c:v>0.28593771284966651</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.10867021704340216</c:v>
+                  <c:v>0.25760315180758414</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.4999240006079955E-2</c:v>
+                  <c:v>0.22519605012951563</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9105,28 +10757,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>1.5417981477864919</c:v>
+                  <c:v>0.73302820880315356</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.1449682462139716</c:v>
+                  <c:v>0.54436050780295864</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.79256887423517097</c:v>
+                  <c:v>0.37681673380385505</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.61567256070531451</c:v>
+                  <c:v>0.29271364415049506</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.41732743510558379</c:v>
+                  <c:v>0.19841299114222519</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.34221729429318443</c:v>
+                  <c:v>0.16270283539861471</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.2655403037072967</c:v>
+                  <c:v>0.1262477409711871</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.22171506952984582</c:v>
+                  <c:v>0.105411593933654</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9204,28 +10856,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>8.3872352988539674E-3</c:v>
+                  <c:v>0.38910722912584877</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.8627536412299268E-3</c:v>
+                  <c:v>0.22559669877380806</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.6459730407098828E-3</c:v>
+                  <c:v>0.12275406633136897</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8473197607055873E-3</c:v>
+                  <c:v>8.5702314026625037E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3917032220712999E-3</c:v>
+                  <c:v>6.4564992540470739E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.6078194809415985E-4</c:v>
+                  <c:v>3.9934074432159364E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.8930529055596609E-4</c:v>
+                  <c:v>3.1978794212041341E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.2163317086198837E-4</c:v>
+                  <c:v>2.4200017109568005E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9278,7 +10930,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -9291,7 +10943,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR"/>
+                  <a:rPr lang="fr-FR" sz="1200"/>
                   <a:t>Nombres de threads</a:t>
                 </a:r>
               </a:p>
@@ -9310,7 +10962,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -9409,7 +11061,7 @@
                   <a:buFontTx/>
                   <a:buNone/>
                   <a:tabLst/>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000">
                         <a:lumMod val="65%"/>
@@ -9422,7 +11074,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:rPr lang="fr-FR" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000">
                         <a:lumMod val="65%"/>
@@ -9462,7 +11114,7 @@
                 <a:buFontTx/>
                 <a:buNone/>
                 <a:tabLst/>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumMod val="65%"/>
@@ -9542,7 +11194,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65%"/>
@@ -9636,16 +11288,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="fr-FR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0%">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65%"/>
-                    <a:lumOff val="35%"/>
-                  </a:sysClr>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>Temps d'exécussion V2 </a:t>
+              <a:rPr lang="fr-FR"/>
+              <a:t>Final Job size affect (17</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="fr-FR" baseline="0%"/>
+              <a:t> villes) - Temps d'exécution</a:t>
+            </a:r>
+            <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -9689,11 +11339,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$B$76</c:f>
+              <c:f>Feuil2!$C$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>18 villes</c:v>
+                  <c:v>final job size @ 10</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9712,7 +11362,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$77:$A$84</c:f>
+              <c:f>Feuil2!$B$14:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -9745,33 +11395,33 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$B$77:$B$84</c:f>
+              <c:f>Feuil2!$C$14:$C$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>227622.6</c:v>
+                  <c:v>66561.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>138852.9</c:v>
+                  <c:v>40910</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>114043.9</c:v>
+                  <c:v>44777.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>91447</c:v>
+                  <c:v>41861.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>85845.4</c:v>
+                  <c:v>51951</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>82812.2</c:v>
+                  <c:v>41849.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>93098.2</c:v>
+                  <c:v>48703</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>87560</c:v>
+                  <c:v>48998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9779,7 +11429,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0AB2-1842-BBA4-D50556DC3F56}"/>
+              <c16:uniqueId val="{00000000-5257-0843-AFA6-939B73D86DBA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9788,11 +11438,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$C$76</c:f>
+              <c:f>Feuil2!$D$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>17 villes</c:v>
+                  <c:v>final job size @ 12</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9811,7 +11461,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$77:$A$84</c:f>
+              <c:f>Feuil2!$B$14:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -9844,33 +11494,33 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$C$77:$C$84</c:f>
+              <c:f>Feuil2!$D$14:$D$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>49581.4</c:v>
+                  <c:v>43179.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26587.4</c:v>
+                  <c:v>21218</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>22472.1</c:v>
+                  <c:v>18042.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>16816.099999999999</c:v>
+                  <c:v>15352.7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18198.900000000001</c:v>
+                  <c:v>16579.3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20725.7</c:v>
+                  <c:v>16088.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>19718.900000000001</c:v>
+                  <c:v>16332.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19737</c:v>
+                  <c:v>15601.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9878,7 +11528,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0AB2-1842-BBA4-D50556DC3F56}"/>
+              <c16:uniqueId val="{00000001-5257-0843-AFA6-939B73D86DBA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9887,11 +11537,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$D$76</c:f>
+              <c:f>Feuil2!$E$13</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>16 villes</c:v>
+                  <c:v>final job size @ 14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9910,7 +11560,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Feuil1!$A$77:$A$84</c:f>
+              <c:f>Feuil2!$B$14:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -9943,33 +11593,33 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Feuil1!$D$77:$D$84</c:f>
+              <c:f>Feuil2!$E$14:$E$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>9728.9</c:v>
+                  <c:v>77776.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6550.4</c:v>
+                  <c:v>82731.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6308.6</c:v>
+                  <c:v>86795.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6090.9</c:v>
+                  <c:v>76857.5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7188.6</c:v>
+                  <c:v>76651.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7305.3</c:v>
+                  <c:v>77266.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8069.8</c:v>
+                  <c:v>76787.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8456.7999999999993</c:v>
+                  <c:v>76897</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9977,205 +11627,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-0AB2-1842-BBA4-D50556DC3F56}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Feuil1!$E$76</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>15 villes</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Feuil1!$A$77:$A$84</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>96</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>192</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>224</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>256</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Feuil1!$E$77:$E$84</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>3725.9</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3213.2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3936.8</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4229.1000000000004</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4490.8999999999996</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6050.7</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6476.5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7488.5</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-0AB2-1842-BBA4-D50556DC3F56}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Feuil1!$F$76</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>14 villes</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Feuil1!$A$77:$A$84</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>96</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>192</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>224</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>256</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Feuil1!$F$77:$F$84</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>884.8</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>743.1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>760</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>846.8</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>888.7</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>988.5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1012.1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1078.8</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-0AB2-1842-BBA4-D50556DC3F56}"/>
+              <c16:uniqueId val="{00000002-5257-0843-AFA6-939B73D86DBA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10187,11 +11639,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1463334015"/>
-        <c:axId val="510930208"/>
+        <c:axId val="248609776"/>
+        <c:axId val="395380336"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1463334015"/>
+        <c:axId val="248609776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="256"/>
@@ -10233,19 +11685,25 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65%"/>
-                        <a:lumOff val="35%"/>
-                      </a:sysClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Nb Threads</a:t>
+                  <a:rPr lang="fr-FR"/>
+                  <a:t>Nombres</a:t>
                 </a:r>
+                <a:r>
+                  <a:rPr lang="fr-FR" baseline="0%"/>
+                  <a:t> de threads</a:t>
+                </a:r>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.43232898213304738"/>
+              <c:y val="0.84101537307836527"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -10312,16 +11770,14 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="510930208"/>
+        <c:crossAx val="395380336"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="510930208"/>
+        <c:axId val="395380336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="230000"/>
-          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -10359,16 +11815,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65%"/>
-                        <a:lumOff val="35%"/>
-                      </a:sysClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Temps [ms]</a:t>
+                  <a:rPr lang="fr-FR"/>
+                  <a:t>Temps d'exécution</a:t>
                 </a:r>
+                <a:r>
+                  <a:rPr lang="fr-FR" baseline="0%"/>
+                  <a:t> [ms]</a:t>
+                </a:r>
+                <a:endParaRPr lang="fr-FR"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -10438,7 +11892,7 @@
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1463334015"/>
+        <c:crossAx val="248609776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -10450,6 +11904,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65%"/>
+                  <a:lumOff val="35%"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -10655,6 +12140,86 @@
 </file>
 
 <file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80%"/>
+    <a:lumOff val="20%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60%"/>
+    <a:lumOff val="40%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70%"/>
+    <a:lumOff val="30%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50%"/>
+    <a:lumOff val="50%"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80%"/>
+    <a:lumOff val="20%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60%"/>
+    <a:lumOff val="40%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70%"/>
+    <a:lumOff val="30%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70%"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50%"/>
+    <a:lumOff val="50%"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors15.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -13560,6 +15125,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25%"/>
+            <a:lumOff val="75%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75%"/>
+        <a:lumOff val="25%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25%"/>
+            <a:lumOff val="75%"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75%"/>
+          <a:lumOff val="25%"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65%"/>
+            <a:lumOff val="35%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35%"/>
+            <a:lumOff val="65%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65%"/>
+            <a:lumOff val="35%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5%"/>
+            <a:lumOff val="95%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50%"/>
+            <a:lumOff val="50%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35%"/>
+            <a:lumOff val="65%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35%"/>
+            <a:lumOff val="65%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0%"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65%"/>
+            <a:lumOff val="35%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25%"/>
+            <a:lumOff val="75%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25%"/>
+            <a:lumOff val="75%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75%"/>
+        <a:lumOff val="25%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25%"/>
+            <a:lumOff val="75%"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75%"/>
+          <a:lumOff val="25%"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65%"/>
+            <a:lumOff val="35%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35%"/>
+            <a:lumOff val="65%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65%"/>
+            <a:lumOff val="35%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15%"/>
+            <a:lumOff val="85%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5%"/>
+            <a:lumOff val="95%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50%"/>
+            <a:lumOff val="50%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35%"/>
+            <a:lumOff val="65%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35%"/>
+            <a:lumOff val="65%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0%"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65%"/>
+            <a:lumOff val="35%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65%"/>
+        <a:lumOff val="35%"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25%"/>
+            <a:lumOff val="75%"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main" id="240">
   <cs:axisTitle>
@@ -17838,16 +20435,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>812036</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>2865</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>189316</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>817471</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>116780</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>408250</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>187335</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17875,15 +20472,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>812800</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>826912</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>197555</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>818235</xdr:colOff>
-      <xdr:row>146</xdr:row>
-      <xdr:rowOff>113915</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>396638</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17912,16 +20509,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>67733</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>118533</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>189088</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>155489</xdr:colOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>61794</xdr:colOff>
       <xdr:row>121</xdr:row>
-      <xdr:rowOff>32028</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17950,16 +20547,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>114072</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>192643</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>396294</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>9198</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>201828</xdr:colOff>
-      <xdr:row>145</xdr:row>
-      <xdr:rowOff>106138</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>42334</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>11923</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17990,6 +20587,85 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Graphique 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C2DA4DB-901E-FEAA-988F-CAFA6C60C48D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://purl.oclc.org/ooxml/drawingml/chart">
+          <c:chart xmlns:c="http://purl.oclc.org/ooxml/drawingml/chart" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Graphique 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25E7728A-E2F8-174E-8A39-30087BEE17A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://purl.oclc.org/ooxml/drawingml/chart">
+          <c:chart xmlns:c="http://purl.oclc.org/ooxml/drawingml/chart" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -19473,7 +22149,7 @@
         <v>37.242800000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>15</v>
       </c>
@@ -19487,7 +22163,7 @@
         <v>34.668700000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>16</v>
       </c>
@@ -19501,7 +22177,7 @@
         <v>23.312000000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>16</v>
       </c>
@@ -19515,7 +22191,7 @@
         <v>30.398</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>16</v>
       </c>
@@ -19529,7 +22205,7 @@
         <v>33.066699999999997</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>16</v>
       </c>
@@ -19543,7 +22219,7 @@
         <v>32.573099999999997</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>16</v>
       </c>
@@ -19556,8 +22232,21 @@
       <c r="D54">
         <v>31.3049</v>
       </c>
+      <c r="I54">
+        <v>10</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+      <c r="K54">
+        <v>21808</v>
+      </c>
+      <c r="L54">
+        <f>K54/1000</f>
+        <v>21.808</v>
+      </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>16</v>
       </c>
@@ -19570,8 +22259,21 @@
       <c r="D55">
         <v>30.747699999999998</v>
       </c>
+      <c r="I55">
+        <v>11</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55">
+        <v>127169.5</v>
+      </c>
+      <c r="L55">
+        <f t="shared" ref="L55:L62" si="0">K55/1000</f>
+        <v>127.1695</v>
+      </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>16</v>
       </c>
@@ -19584,8 +22286,21 @@
       <c r="D56">
         <v>31.871300000000002</v>
       </c>
+      <c r="I56">
+        <v>12</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56">
+        <v>582304</v>
+      </c>
+      <c r="L56">
+        <f t="shared" si="0"/>
+        <v>582.30399999999997</v>
+      </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>16</v>
       </c>
@@ -19598,8 +22313,21 @@
       <c r="D57">
         <v>31.85</v>
       </c>
+      <c r="I57">
+        <v>13</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57">
+        <v>3992203</v>
+      </c>
+      <c r="L57">
+        <f t="shared" si="0"/>
+        <v>3992.203</v>
+      </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>17</v>
       </c>
@@ -19612,8 +22340,21 @@
       <c r="D58">
         <v>2.5644</v>
       </c>
+      <c r="I58">
+        <v>14</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58">
+        <v>8622345.5</v>
+      </c>
+      <c r="L58">
+        <f t="shared" si="0"/>
+        <v>8622.3454999999994</v>
+      </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>17</v>
       </c>
@@ -19626,8 +22367,21 @@
       <c r="D59">
         <v>8.2820999999999998</v>
       </c>
+      <c r="I59">
+        <v>15</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59">
+        <v>46392788</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="0"/>
+        <v>46392.788</v>
+      </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>17</v>
       </c>
@@ -19640,8 +22394,21 @@
       <c r="D60">
         <v>7.6848000000000001</v>
       </c>
+      <c r="I60">
+        <v>16</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60">
+        <v>228209860.5</v>
+      </c>
+      <c r="L60">
+        <f t="shared" si="0"/>
+        <v>228209.86050000001</v>
+      </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>17</v>
       </c>
@@ -19654,8 +22421,21 @@
       <c r="D61">
         <v>15.569000000000001</v>
       </c>
+      <c r="I61">
+        <v>17</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61">
+        <v>1137841777</v>
+      </c>
+      <c r="L61">
+        <f t="shared" si="0"/>
+        <v>1137841.777</v>
+      </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="19" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>17</v>
       </c>
@@ -19668,8 +22448,21 @@
       <c r="D62">
         <v>16.438300000000002</v>
       </c>
+      <c r="I62">
+        <v>18</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62" s="2">
+        <v>6541797620</v>
+      </c>
+      <c r="L62">
+        <f t="shared" si="0"/>
+        <v>6541797.6200000001</v>
+      </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>17</v>
       </c>
@@ -19683,7 +22476,7 @@
         <v>18.258600000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>17</v>
       </c>
@@ -19960,7 +22753,7 @@
         <v>271.39999999999998</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>160</v>
       </c>
@@ -19986,7 +22779,7 @@
         <v>299.7</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>192</v>
       </c>
@@ -20012,7 +22805,7 @@
         <v>332.1</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>224</v>
       </c>
@@ -20038,7 +22831,7 @@
         <v>352.1</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>256</v>
       </c>
@@ -20064,30 +22857,48 @@
         <v>374.3</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>21</v>
       </c>
       <c r="B87">
-        <v>5000000</v>
+        <f>L62</f>
+        <v>6541797.6200000001</v>
       </c>
       <c r="C87">
-        <v>480000</v>
+        <f>L61</f>
+        <v>1137841.777</v>
       </c>
       <c r="D87">
-        <v>480000</v>
+        <f>L60</f>
+        <v>228209.86050000001</v>
       </c>
       <c r="E87">
-        <v>1000</v>
+        <f>L59</f>
+        <v>46392.788</v>
       </c>
       <c r="F87">
-        <v>1000</v>
-      </c>
-      <c r="G87">
-        <v>1000</v>
+        <f>L58</f>
+        <v>8622.3454999999994</v>
+      </c>
+      <c r="G87" s="3">
+        <f>L57</f>
+        <v>3992.203</v>
+      </c>
+      <c r="H87">
+        <f>L56</f>
+        <v>582.30399999999997</v>
+      </c>
+      <c r="I87">
+        <f>L55</f>
+        <v>127.1695</v>
+      </c>
+      <c r="J87">
+        <f>L54</f>
+        <v>21.808</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
         <v>4</v>
       </c>
@@ -20107,207 +22918,207 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>32</v>
       </c>
       <c r="B90">
         <f>B$87/B77</f>
-        <v>22.853225161400903</v>
+        <v>29.90023479403531</v>
       </c>
       <c r="C90">
-        <f t="shared" ref="C90:G90" si="0">C$87/C77</f>
-        <v>11.116489227427158</v>
+        <f t="shared" ref="C90:G90" si="1">C$87/C77</f>
+        <v>26.351678867785573</v>
       </c>
       <c r="D90">
         <f>D$87/D77</f>
-        <v>52.34973988722993</v>
+        <v>24.889014243491729</v>
       </c>
       <c r="E90">
-        <f t="shared" si="0"/>
-        <v>0.2971150132216181</v>
+        <f t="shared" si="1"/>
+        <v>13.783993820007726</v>
       </c>
       <c r="F90">
-        <f t="shared" si="0"/>
-        <v>1.2615112905260502</v>
+        <f t="shared" si="1"/>
+        <v>10.877186199066481</v>
       </c>
       <c r="G90">
-        <f t="shared" si="0"/>
-        <v>2.3057412958266084</v>
+        <f t="shared" si="1"/>
+        <v>9.204987318422873</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>64</v>
       </c>
       <c r="B91">
-        <f t="shared" ref="B91:C97" si="1">B$87/B78</f>
-        <v>44.972643141177223</v>
+        <f t="shared" ref="B91:C97" si="2">B$87/B78</f>
+        <v>58.840385973212499</v>
       </c>
       <c r="C91">
-        <f t="shared" si="1"/>
-        <v>22.622301819210104</v>
+        <f t="shared" si="2"/>
+        <v>53.626250212084081</v>
       </c>
       <c r="D91">
-        <f t="shared" ref="D91:G97" si="2">D$87/D78</f>
-        <v>82.592012664108609</v>
+        <f t="shared" ref="D91:G97" si="3">D$87/D78</f>
+        <v>39.267316017688458</v>
       </c>
       <c r="E91">
-        <f t="shared" si="2"/>
-        <v>0.34522042324023894</v>
+        <f t="shared" si="3"/>
+        <v>16.015737908654678</v>
       </c>
       <c r="F91">
-        <f t="shared" si="2"/>
-        <v>1.4585764294049008</v>
+        <f t="shared" si="3"/>
+        <v>12.576349912485414</v>
       </c>
       <c r="G91">
-        <f t="shared" si="2"/>
-        <v>2.4838549428713361</v>
+        <f t="shared" si="3"/>
+        <v>9.916053154495776</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>96</v>
       </c>
       <c r="B92">
-        <f t="shared" si="1"/>
-        <v>46.442547317989337</v>
+        <f t="shared" si="2"/>
+        <v>60.763549102312005</v>
       </c>
       <c r="C92">
-        <f t="shared" si="1"/>
-        <v>26.604294376517274</v>
+        <f t="shared" si="2"/>
+        <v>63.065578310849006</v>
       </c>
       <c r="D92">
-        <f t="shared" si="2"/>
-        <v>96.148068024758118</v>
+        <f t="shared" si="3"/>
+        <v>45.712369148488676</v>
       </c>
       <c r="E92">
-        <f t="shared" si="2"/>
-        <v>0.35799949880070164</v>
+        <f t="shared" si="3"/>
+        <v>16.608594851967208</v>
       </c>
       <c r="F92">
-        <f t="shared" si="2"/>
-        <v>1.405678942929435</v>
+        <f t="shared" si="3"/>
+        <v>12.120249508012369</v>
       </c>
       <c r="G92">
-        <f t="shared" si="2"/>
-        <v>2.3551577955723033</v>
+        <f t="shared" si="3"/>
+        <v>9.4022680169571355</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>128</v>
       </c>
       <c r="B93">
-        <f t="shared" si="1"/>
-        <v>64.046400336115511</v>
+        <f t="shared" si="2"/>
+        <v>83.795717857673537</v>
       </c>
       <c r="C93">
-        <f t="shared" si="1"/>
-        <v>31.264858949891547</v>
+        <f t="shared" si="2"/>
+        <v>74.113463885831152</v>
       </c>
       <c r="D93">
-        <f t="shared" si="2"/>
-        <v>102.18418699706221</v>
+        <f t="shared" si="3"/>
+        <v>48.582164708136425</v>
       </c>
       <c r="E93">
-        <f t="shared" si="2"/>
-        <v>0.35944071025484348</v>
+        <f t="shared" si="3"/>
+        <v>16.675456669422381</v>
       </c>
       <c r="F93">
-        <f t="shared" si="2"/>
-        <v>1.2230919765166339</v>
+        <f t="shared" si="3"/>
+        <v>10.545921599804304</v>
       </c>
       <c r="G93">
-        <f t="shared" si="2"/>
-        <v>2.0872469213107911</v>
+        <f t="shared" si="3"/>
+        <v>8.3327134209977043</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>160</v>
       </c>
       <c r="B94">
-        <f t="shared" si="1"/>
-        <v>63.660288330177913</v>
+        <f t="shared" si="2"/>
+        <v>83.290544537374331</v>
       </c>
       <c r="C94">
-        <f t="shared" si="1"/>
-        <v>28.951765152931667</v>
+        <f t="shared" si="2"/>
+        <v>68.630266476871768</v>
       </c>
       <c r="D94">
-        <f t="shared" si="2"/>
-        <v>104.90656758824173</v>
+        <f t="shared" si="3"/>
+        <v>49.876485739263472</v>
       </c>
       <c r="E94">
-        <f t="shared" si="2"/>
-        <v>0.36016567621105711</v>
+        <f t="shared" si="3"/>
+        <v>16.709089861336214</v>
       </c>
       <c r="F94">
-        <f t="shared" si="2"/>
-        <v>1.1627906976744187</v>
+        <f t="shared" si="3"/>
+        <v>10.025983139534883</v>
       </c>
       <c r="G94">
-        <f t="shared" si="2"/>
-        <v>1.9719976336028395</v>
+        <f t="shared" si="3"/>
+        <v>7.8726148688621569</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>192</v>
       </c>
       <c r="B95">
-        <f t="shared" si="1"/>
-        <v>63.575377510591657</v>
+        <f t="shared" si="2"/>
+        <v>83.179450657878007</v>
       </c>
       <c r="C95">
-        <f t="shared" si="1"/>
-        <v>29.834418974690468</v>
+        <f t="shared" si="2"/>
+        <v>70.722600629009008</v>
       </c>
       <c r="D95">
-        <f t="shared" si="2"/>
-        <v>110.57105341964018</v>
+        <f t="shared" si="3"/>
+        <v>52.569593075487781</v>
       </c>
       <c r="E95">
-        <f t="shared" si="2"/>
-        <v>0.3582046781530967</v>
+        <f t="shared" si="3"/>
+        <v>16.618113694164848</v>
       </c>
       <c r="F95">
-        <f t="shared" si="2"/>
-        <v>1.0358400662937643</v>
+        <f t="shared" si="3"/>
+        <v>8.9313709343277399</v>
       </c>
       <c r="G95">
-        <f t="shared" si="2"/>
-        <v>1.7699115044247788</v>
+        <f t="shared" si="3"/>
+        <v>7.0658460176991147</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>224</v>
       </c>
       <c r="B96">
-        <f t="shared" si="1"/>
-        <v>67.13707376350294</v>
+        <f t="shared" si="2"/>
+        <v>87.8394298719696</v>
       </c>
       <c r="C96">
-        <f t="shared" si="1"/>
-        <v>29.389434498297863</v>
+        <f t="shared" si="2"/>
+        <v>69.667763280350712</v>
       </c>
       <c r="D96">
-        <f t="shared" si="2"/>
-        <v>114.19870574800153</v>
+        <f t="shared" si="3"/>
+        <v>54.294313975066622</v>
       </c>
       <c r="E96">
-        <f t="shared" si="2"/>
-        <v>0.35573263135427413</v>
+        <f t="shared" si="3"/>
+        <v>16.503428551100992</v>
       </c>
       <c r="F96">
-        <f t="shared" si="2"/>
-        <v>0.98260784121057276</v>
+        <f t="shared" si="3"/>
+        <v>8.4723842979266966</v>
       </c>
       <c r="G96">
-        <f t="shared" si="2"/>
-        <v>1.6722408026755853</v>
+        <f t="shared" si="3"/>
+        <v>6.6759247491638796</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
@@ -20315,28 +23126,28 @@
         <v>256</v>
       </c>
       <c r="B97">
-        <f t="shared" si="1"/>
-        <v>64.69560716827327</v>
+        <f t="shared" si="2"/>
+        <v>84.645113799573011</v>
       </c>
       <c r="C97">
-        <f t="shared" si="1"/>
-        <v>30.766666880324077</v>
+        <f t="shared" si="2"/>
+        <v>72.932497740572899</v>
       </c>
       <c r="D97">
-        <f t="shared" si="2"/>
-        <v>115.01413715435856</v>
+        <f t="shared" si="3"/>
+        <v>54.682000407341739</v>
       </c>
       <c r="E97">
-        <f t="shared" si="2"/>
-        <v>0.35778175313059035</v>
+        <f t="shared" si="3"/>
+        <v>16.598493023255813</v>
       </c>
       <c r="F97">
-        <f t="shared" si="2"/>
-        <v>0.90752336872674466</v>
+        <f t="shared" si="3"/>
+        <v>7.8249800344858871</v>
       </c>
       <c r="G97">
-        <f t="shared" si="2"/>
-        <v>1.5351550506601168</v>
+        <f t="shared" si="3"/>
+        <v>6.12865059871047</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
@@ -20368,27 +23179,27 @@
       </c>
       <c r="B100">
         <f>B90/$A100</f>
-        <v>0.71416328629377823</v>
+        <v>0.93438233731360343</v>
       </c>
       <c r="C100">
-        <f t="shared" ref="C100:G100" si="3">C90/$A100</f>
-        <v>0.34739028835709868</v>
+        <f t="shared" ref="C100:F100" si="4">C90/$A100</f>
+        <v>0.82348996461829915</v>
       </c>
       <c r="D100">
-        <f t="shared" si="3"/>
-        <v>1.6359293714759353</v>
+        <f t="shared" si="4"/>
+        <v>0.77778169510911654</v>
       </c>
       <c r="E100">
-        <f t="shared" si="3"/>
-        <v>9.2848441631755655E-3</v>
+        <f t="shared" si="4"/>
+        <v>0.43074980687524145</v>
       </c>
       <c r="F100">
-        <f t="shared" si="3"/>
-        <v>3.9422227828939067E-2</v>
+        <f t="shared" si="4"/>
+        <v>0.33991206872082752</v>
       </c>
       <c r="G100">
         <f>G90/$A100</f>
-        <v>7.2054415494581511E-2</v>
+        <v>0.28765585370071478</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
@@ -20396,28 +23207,28 @@
         <v>64</v>
       </c>
       <c r="B101">
-        <f t="shared" ref="B101:G107" si="4">B91/$A101</f>
-        <v>0.7026975490808941</v>
+        <f t="shared" ref="B101:G107" si="5">B91/$A101</f>
+        <v>0.91938103083144529</v>
       </c>
       <c r="C101">
-        <f t="shared" si="4"/>
-        <v>0.35347346592515788</v>
+        <f t="shared" si="5"/>
+        <v>0.83791015956381376</v>
       </c>
       <c r="D101">
-        <f t="shared" si="4"/>
-        <v>1.290500197876697</v>
+        <f t="shared" si="5"/>
+        <v>0.61355181277638215</v>
       </c>
       <c r="E101">
-        <f t="shared" si="4"/>
-        <v>5.3940691131287334E-3</v>
+        <f t="shared" si="5"/>
+        <v>0.25024590482272935</v>
       </c>
       <c r="F101">
-        <f t="shared" si="4"/>
-        <v>2.2790256709451576E-2</v>
+        <f t="shared" si="5"/>
+        <v>0.19650546738258459</v>
       </c>
       <c r="G101">
-        <f t="shared" si="4"/>
-        <v>3.8810233482364627E-2</v>
+        <f t="shared" si="5"/>
+        <v>0.1549383305389965</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
@@ -20425,28 +23236,28 @@
         <v>96</v>
       </c>
       <c r="B102">
-        <f t="shared" si="4"/>
-        <v>0.48377653456238895</v>
+        <f t="shared" si="5"/>
+        <v>0.63295363648241676</v>
       </c>
       <c r="C102">
-        <f t="shared" si="4"/>
-        <v>0.27712806642205495</v>
+        <f t="shared" si="5"/>
+        <v>0.65693310740467714</v>
       </c>
       <c r="D102">
-        <f t="shared" si="4"/>
-        <v>1.0015423752578971</v>
+        <f t="shared" si="5"/>
+        <v>0.47617051196342369</v>
       </c>
       <c r="E102">
-        <f t="shared" si="4"/>
-        <v>3.7291614458406421E-3</v>
+        <f t="shared" si="5"/>
+        <v>0.17300619637465842</v>
       </c>
       <c r="F102">
-        <f t="shared" si="4"/>
-        <v>1.4642488988848281E-2</v>
+        <f t="shared" si="5"/>
+        <v>0.1262525990417955</v>
       </c>
       <c r="G102">
-        <f t="shared" si="4"/>
-        <v>2.4532893703878161E-2</v>
+        <f t="shared" si="5"/>
+        <v>9.7940291843303495E-2</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
@@ -20454,28 +23265,28 @@
         <v>128</v>
       </c>
       <c r="B103">
-        <f t="shared" si="4"/>
-        <v>0.50036250262590243</v>
+        <f t="shared" si="5"/>
+        <v>0.65465404576307451</v>
       </c>
       <c r="C103">
-        <f t="shared" si="4"/>
-        <v>0.24425671054602771</v>
+        <f t="shared" si="5"/>
+        <v>0.57901143660805587</v>
       </c>
       <c r="D103">
-        <f t="shared" si="4"/>
-        <v>0.79831396091454854</v>
+        <f t="shared" si="5"/>
+        <v>0.37954816178231582</v>
       </c>
       <c r="E103">
-        <f t="shared" si="4"/>
-        <v>2.8081305488659647E-3</v>
+        <f t="shared" si="5"/>
+        <v>0.13027700522986235</v>
       </c>
       <c r="F103">
-        <f t="shared" si="4"/>
-        <v>9.5554060665362026E-3</v>
+        <f t="shared" si="5"/>
+        <v>8.2390012498471124E-2</v>
       </c>
       <c r="G103">
-        <f t="shared" si="4"/>
-        <v>1.6306616572740556E-2</v>
+        <f t="shared" si="5"/>
+        <v>6.5099323601544565E-2</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
@@ -20483,28 +23294,28 @@
         <v>160</v>
       </c>
       <c r="B104">
-        <f t="shared" si="4"/>
-        <v>0.39787680206361198</v>
+        <f t="shared" si="5"/>
+        <v>0.52056590335858954</v>
       </c>
       <c r="C104">
-        <f t="shared" si="4"/>
-        <v>0.18094853220582291</v>
+        <f t="shared" si="5"/>
+        <v>0.42893916548044853</v>
       </c>
       <c r="D104">
-        <f t="shared" si="4"/>
-        <v>0.6556660474265108</v>
+        <f t="shared" si="5"/>
+        <v>0.31172803587039671</v>
       </c>
       <c r="E104">
-        <f t="shared" si="4"/>
-        <v>2.2510354763191067E-3</v>
+        <f t="shared" si="5"/>
+        <v>0.10443181163335133</v>
       </c>
       <c r="F104">
-        <f t="shared" si="4"/>
-        <v>7.267441860465117E-3</v>
+        <f t="shared" si="5"/>
+        <v>6.2662394622093026E-2</v>
       </c>
       <c r="G104">
-        <f t="shared" si="4"/>
-        <v>1.2324985210017746E-2</v>
+        <f t="shared" si="5"/>
+        <v>4.9203842930388479E-2</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.2">
@@ -20512,28 +23323,28 @@
         <v>192</v>
       </c>
       <c r="B105">
-        <f t="shared" si="4"/>
-        <v>0.3311217578676649</v>
+        <f t="shared" si="5"/>
+        <v>0.43322630550978131</v>
       </c>
       <c r="C105">
-        <f t="shared" si="4"/>
-        <v>0.15538759882651285</v>
+        <f t="shared" si="5"/>
+        <v>0.36834687827608859</v>
       </c>
       <c r="D105">
-        <f t="shared" si="4"/>
-        <v>0.57589090322729264</v>
+        <f t="shared" si="5"/>
+        <v>0.27379996393483219</v>
       </c>
       <c r="E105">
-        <f t="shared" si="4"/>
-        <v>1.8656493653807121E-3</v>
+        <f t="shared" si="5"/>
+        <v>8.6552675490441919E-2</v>
       </c>
       <c r="F105">
-        <f t="shared" si="4"/>
-        <v>5.3950003452800229E-3</v>
+        <f t="shared" si="5"/>
+        <v>4.6517556949623645E-2</v>
       </c>
       <c r="G105">
-        <f t="shared" si="4"/>
-        <v>9.2182890855457226E-3</v>
+        <f t="shared" si="5"/>
+        <v>3.6801281342182891E-2</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.2">
@@ -20541,28 +23352,28 @@
         <v>224</v>
       </c>
       <c r="B106">
-        <f t="shared" si="4"/>
-        <v>0.29971907930135239</v>
+        <f t="shared" si="5"/>
+        <v>0.39214031192843574</v>
       </c>
       <c r="C106">
-        <f t="shared" si="4"/>
-        <v>0.13120283258168688</v>
+        <f t="shared" si="5"/>
+        <v>0.31101680035870855</v>
       </c>
       <c r="D106">
-        <f t="shared" si="4"/>
-        <v>0.5098156506607211</v>
+        <f t="shared" si="5"/>
+        <v>0.24238533024583314</v>
       </c>
       <c r="E106">
-        <f t="shared" si="4"/>
-        <v>1.5880921042601523E-3</v>
+        <f t="shared" si="5"/>
+        <v>7.3676020317415145E-2</v>
       </c>
       <c r="F106">
-        <f t="shared" si="4"/>
-        <v>4.3866421482614852E-3</v>
+        <f t="shared" si="5"/>
+        <v>3.7823144187172753E-2</v>
       </c>
       <c r="G106">
-        <f t="shared" si="4"/>
-        <v>7.4653607262302911E-3</v>
+        <f t="shared" si="5"/>
+        <v>2.9803235487338747E-2</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.2">
@@ -20570,28 +23381,28 @@
         <v>256</v>
       </c>
       <c r="B107">
-        <f t="shared" si="4"/>
-        <v>0.25271721550106746</v>
+        <f t="shared" si="5"/>
+        <v>0.33064497577958207</v>
       </c>
       <c r="C107">
-        <f t="shared" si="4"/>
-        <v>0.12018229250126593</v>
+        <f t="shared" si="5"/>
+        <v>0.28489256929911289</v>
       </c>
       <c r="D107">
-        <f t="shared" si="4"/>
-        <v>0.44927397325921314</v>
+        <f t="shared" si="5"/>
+        <v>0.21360156409117867</v>
       </c>
       <c r="E107">
-        <f t="shared" si="4"/>
-        <v>1.3975849731663686E-3</v>
+        <f t="shared" si="5"/>
+        <v>6.4837863372093019E-2</v>
       </c>
       <c r="F107">
-        <f t="shared" si="4"/>
-        <v>3.5450131590888463E-3</v>
+        <f t="shared" si="5"/>
+        <v>3.0566328259710496E-2</v>
       </c>
       <c r="G107">
-        <f t="shared" si="4"/>
-        <v>5.9966994166410813E-3</v>
+        <f t="shared" si="5"/>
+        <v>2.3940041401212774E-2</v>
       </c>
     </row>
     <row r="130" spans="19:19" x14ac:dyDescent="0.2">
@@ -20599,11 +23410,361 @@
     </row>
   </sheetData>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA4A4FA4-9FC3-E34A-9686-80F9E17BDBA3}">
+  <dimension ref="A12:E32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>32</v>
+      </c>
+      <c r="C14">
+        <v>66561.5</v>
+      </c>
+      <c r="D14">
+        <v>43179.1</v>
+      </c>
+      <c r="E14">
+        <v>77776.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>17</v>
+      </c>
+      <c r="B15">
+        <v>64</v>
+      </c>
+      <c r="C15">
+        <v>40910</v>
+      </c>
+      <c r="D15">
+        <v>21218</v>
+      </c>
+      <c r="E15">
+        <v>82731.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>96</v>
+      </c>
+      <c r="C16">
+        <v>44777.5</v>
+      </c>
+      <c r="D16">
+        <v>18042.2</v>
+      </c>
+      <c r="E16">
+        <v>86795.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>128</v>
+      </c>
+      <c r="C17">
+        <v>41861.5</v>
+      </c>
+      <c r="D17">
+        <v>15352.7</v>
+      </c>
+      <c r="E17">
+        <v>76857.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>160</v>
+      </c>
+      <c r="C18">
+        <v>51951</v>
+      </c>
+      <c r="D18">
+        <v>16579.3</v>
+      </c>
+      <c r="E18">
+        <v>76651.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>192</v>
+      </c>
+      <c r="C19">
+        <v>41849.5</v>
+      </c>
+      <c r="D19">
+        <v>16088.8</v>
+      </c>
+      <c r="E19">
+        <v>77266.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20">
+        <v>224</v>
+      </c>
+      <c r="C20">
+        <v>48703</v>
+      </c>
+      <c r="D20">
+        <v>16332.4</v>
+      </c>
+      <c r="E20">
+        <v>76787.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>17</v>
+      </c>
+      <c r="B21">
+        <v>256</v>
+      </c>
+      <c r="C21">
+        <v>48998</v>
+      </c>
+      <c r="D21">
+        <v>15601.3</v>
+      </c>
+      <c r="E21">
+        <v>76897</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>12</v>
+      </c>
+      <c r="E23">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>17</v>
+      </c>
+      <c r="B25">
+        <v>32</v>
+      </c>
+      <c r="C25">
+        <v>1.8708</v>
+      </c>
+      <c r="D25">
+        <v>2.5644</v>
+      </c>
+      <c r="E25">
+        <v>5638.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>17</v>
+      </c>
+      <c r="B26">
+        <v>64</v>
+      </c>
+      <c r="C26">
+        <v>4.3811</v>
+      </c>
+      <c r="D26">
+        <v>8.2820999999999998</v>
+      </c>
+      <c r="E26">
+        <v>6035.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>17</v>
+      </c>
+      <c r="B27">
+        <v>96</v>
+      </c>
+      <c r="C27">
+        <v>5.6226000000000003</v>
+      </c>
+      <c r="D27">
+        <v>7.6848000000000001</v>
+      </c>
+      <c r="E27">
+        <v>6483.35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>17</v>
+      </c>
+      <c r="B28">
+        <v>128</v>
+      </c>
+      <c r="C28">
+        <v>45.640500000000003</v>
+      </c>
+      <c r="D28">
+        <v>15.569000000000001</v>
+      </c>
+      <c r="E28">
+        <v>5022</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>17</v>
+      </c>
+      <c r="B29">
+        <v>160</v>
+      </c>
+      <c r="C29">
+        <v>14.946099999999999</v>
+      </c>
+      <c r="D29">
+        <v>16.438300000000002</v>
+      </c>
+      <c r="E29">
+        <v>4718.16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>17</v>
+      </c>
+      <c r="B30">
+        <v>192</v>
+      </c>
+      <c r="C30">
+        <v>21.526299999999999</v>
+      </c>
+      <c r="D30">
+        <v>18.258600000000001</v>
+      </c>
+      <c r="E30">
+        <v>4502.5249999999996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>17</v>
+      </c>
+      <c r="B31">
+        <v>224</v>
+      </c>
+      <c r="C31">
+        <v>25.939</v>
+      </c>
+      <c r="D31">
+        <v>18.699100000000001</v>
+      </c>
+      <c r="E31">
+        <v>4364.9049999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>17</v>
+      </c>
+      <c r="B32">
+        <v>256</v>
+      </c>
+      <c r="C32">
+        <v>30.686699999999998</v>
+      </c>
+      <c r="D32">
+        <v>20.902999999999999</v>
+      </c>
+      <c r="E32">
+        <v>4211.7749999999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6125351D-81E3-1A46-BB3E-E93BB876974E}">
   <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -21949,7 +25110,7 @@
         <v>846.8</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>160</v>
       </c>
@@ -21969,7 +25130,7 @@
         <v>888.7</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>192</v>
       </c>
@@ -21989,7 +25150,7 @@
         <v>988.5</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>224</v>
       </c>
@@ -22009,7 +25170,7 @@
         <v>1012.1</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>256</v>
       </c>
@@ -22029,7 +25190,7 @@
         <v>1078.8</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B85">
         <f>MIN(B77:B84)</f>
         <v>82812.2</v>
@@ -22051,30 +25212,39 @@
         <v>743.1</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>21</v>
       </c>
       <c r="B87">
-        <v>5000000</v>
+        <v>6541797.6200000001</v>
       </c>
       <c r="C87">
-        <v>480000</v>
+        <v>1137841.777</v>
       </c>
       <c r="D87">
-        <v>480000</v>
+        <v>228209.86050000001</v>
       </c>
       <c r="E87">
-        <v>1000</v>
+        <v>46392.788</v>
       </c>
       <c r="F87">
-        <v>1000</v>
+        <v>8622.3454999999994</v>
       </c>
       <c r="G87">
-        <v>1000</v>
+        <v>3992.203</v>
+      </c>
+      <c r="H87">
+        <v>582.30399999999997</v>
+      </c>
+      <c r="I87">
+        <v>127.1695</v>
+      </c>
+      <c r="J87">
+        <v>21.808</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
         <v>4</v>
       </c>
@@ -22094,203 +25264,203 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>32</v>
       </c>
       <c r="B90">
         <f>B$87/B77</f>
-        <v>21.966184377122481</v>
+        <v>28.739666535748206</v>
       </c>
       <c r="C90">
         <f t="shared" ref="C90:G90" si="1">C$87/C77</f>
-        <v>9.6810497484943951</v>
+        <v>22.948964268858887</v>
       </c>
       <c r="D90">
         <f>D$87/D77</f>
-        <v>49.337540729167742</v>
+        <v>23.456902681700914</v>
       </c>
       <c r="E90">
         <f t="shared" si="1"/>
-        <v>0.26839152956332696</v>
+        <v>12.451431332027161</v>
       </c>
       <c r="F90">
         <f t="shared" si="1"/>
-        <v>1.1301989150090417</v>
+        <v>9.7449655289330916</v>
       </c>
       <c r="G90" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>64</v>
       </c>
       <c r="B91">
         <f t="shared" ref="B91:G97" si="2">B$87/B78</f>
-        <v>36.009330737780772</v>
+        <v>47.113150823641426</v>
       </c>
       <c r="C91">
         <f t="shared" si="2"/>
-        <v>18.053664517779097</v>
+        <v>42.796278575565864</v>
       </c>
       <c r="D91">
         <f t="shared" si="2"/>
-        <v>73.277967757694185</v>
+        <v>34.839072499389353</v>
       </c>
       <c r="E91">
         <f t="shared" si="2"/>
-        <v>0.31121623303871532</v>
+        <v>14.438188721523716</v>
       </c>
       <c r="F91">
         <f t="shared" si="2"/>
-        <v>1.3457139012245996</v>
+        <v>11.60321020051137</v>
       </c>
       <c r="G91" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>96</v>
       </c>
       <c r="B92">
         <f t="shared" si="2"/>
-        <v>43.84276581211271</v>
+        <v>57.362100208779253</v>
       </c>
       <c r="C92">
         <f t="shared" si="2"/>
-        <v>21.359819509525146</v>
+        <v>50.633531223161171</v>
       </c>
       <c r="D92">
         <f t="shared" si="2"/>
-        <v>76.08661192657641</v>
+        <v>36.174406445170085</v>
       </c>
       <c r="E92">
         <f t="shared" si="2"/>
-        <v>0.25401341190814875</v>
+        <v>11.784390367811421</v>
       </c>
       <c r="F92">
         <f t="shared" si="2"/>
-        <v>1.3157894736842106</v>
+        <v>11.345191447368419</v>
       </c>
       <c r="G92" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>128</v>
       </c>
       <c r="B93">
         <f t="shared" si="2"/>
-        <v>54.676479272146707</v>
+        <v>71.536492394501735</v>
       </c>
       <c r="C93">
         <f t="shared" si="2"/>
-        <v>28.544073834004319</v>
+        <v>67.663832696047251</v>
       </c>
       <c r="D93">
         <f t="shared" si="2"/>
-        <v>78.806087770280257</v>
+        <v>37.467346451263367</v>
       </c>
       <c r="E93">
         <f t="shared" si="2"/>
-        <v>0.23645692937031518</v>
+        <v>10.969896195408005</v>
       </c>
       <c r="F93">
         <f t="shared" si="2"/>
-        <v>1.1809163911195089</v>
+        <v>10.182269130845537</v>
       </c>
       <c r="G93" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>160</v>
       </c>
       <c r="B94">
         <f t="shared" si="2"/>
-        <v>58.24423906231435</v>
+        <v>76.204404895311811</v>
       </c>
       <c r="C94">
         <f t="shared" si="2"/>
-        <v>26.375220480358699</v>
+        <v>62.522557791954455</v>
       </c>
       <c r="D94">
         <f t="shared" si="2"/>
-        <v>66.772389616893406</v>
+        <v>31.746078582756031</v>
       </c>
       <c r="E94">
         <f t="shared" si="2"/>
-        <v>0.22267251553140799</v>
+        <v>10.330398806475317</v>
       </c>
       <c r="F94">
         <f t="shared" si="2"/>
-        <v>1.1252391133115787</v>
+        <v>9.7022004050860797</v>
       </c>
       <c r="G94" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>192</v>
       </c>
       <c r="B95">
         <f t="shared" si="2"/>
-        <v>60.377577216883502</v>
+        <v>78.995578187754944</v>
       </c>
       <c r="C95">
         <f t="shared" si="2"/>
-        <v>23.159652026228304</v>
+        <v>54.900040867135971</v>
       </c>
       <c r="D95">
         <f t="shared" si="2"/>
-        <v>65.705720504291406</v>
+        <v>31.238944396534023</v>
       </c>
       <c r="E95">
         <f t="shared" si="2"/>
-        <v>0.1652701340340787</v>
+        <v>7.6673422909745979</v>
       </c>
       <c r="F95">
         <f t="shared" si="2"/>
-        <v>1.0116337885685383</v>
+        <v>8.7226560445118864</v>
       </c>
       <c r="G95" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>224</v>
       </c>
       <c r="B96">
         <f t="shared" si="2"/>
-        <v>53.706731172031255</v>
+        <v>70.267713231834776</v>
       </c>
       <c r="C96">
         <f t="shared" si="2"/>
-        <v>24.342128617722082</v>
+        <v>57.703106004898849</v>
       </c>
       <c r="D96">
         <f t="shared" si="2"/>
-        <v>59.481028030434459</v>
+        <v>28.279493977545911</v>
       </c>
       <c r="E96">
         <f t="shared" si="2"/>
-        <v>0.15440438508453641</v>
+        <v>7.1632499034972597</v>
       </c>
       <c r="F96">
         <f t="shared" si="2"/>
-        <v>0.98804465961861476</v>
+        <v>8.5192624246615942</v>
       </c>
       <c r="G96" t="e">
         <f t="shared" si="2"/>
@@ -22303,23 +25473,23 @@
       </c>
       <c r="B97">
         <f t="shared" si="2"/>
-        <v>57.103700319780721</v>
+        <v>74.712170169026948</v>
       </c>
       <c r="C97">
         <f t="shared" si="2"/>
-        <v>24.319805441556468</v>
+        <v>57.650188833156001</v>
       </c>
       <c r="D97">
         <f t="shared" si="2"/>
-        <v>56.75905779964053</v>
+        <v>26.985368047015424</v>
       </c>
       <c r="E97">
         <f t="shared" si="2"/>
-        <v>0.13353809174066902</v>
+        <v>6.1952043800494092</v>
       </c>
       <c r="F97">
         <f t="shared" si="2"/>
-        <v>0.9269558769002596</v>
+        <v>7.9925338338895067</v>
       </c>
       <c r="G97" t="e">
         <f t="shared" si="2"/>
@@ -22355,23 +25525,23 @@
       </c>
       <c r="B100">
         <f>B90/$A100</f>
-        <v>0.68644326178507753</v>
+        <v>0.89811457924213145</v>
       </c>
       <c r="C100">
-        <f t="shared" ref="C100:G100" si="3">C90/$A100</f>
-        <v>0.30253280464044985</v>
+        <f t="shared" ref="C100:F100" si="3">C90/$A100</f>
+        <v>0.71715513340184023</v>
       </c>
       <c r="D100">
         <f t="shared" si="3"/>
-        <v>1.5417981477864919</v>
+        <v>0.73302820880315356</v>
       </c>
       <c r="E100">
         <f t="shared" si="3"/>
-        <v>8.3872352988539674E-3</v>
+        <v>0.38910722912584877</v>
       </c>
       <c r="F100">
         <f t="shared" si="3"/>
-        <v>3.5318716094032553E-2</v>
+        <v>0.30453017277915911</v>
       </c>
       <c r="G100" t="e">
         <f>G90/$A100</f>
@@ -22384,23 +25554,23 @@
       </c>
       <c r="B101">
         <f t="shared" ref="B101:G107" si="4">B91/$A101</f>
-        <v>0.56264579277782456</v>
+        <v>0.73614298161939729</v>
       </c>
       <c r="C101">
         <f t="shared" si="4"/>
-        <v>0.2820885080902984</v>
+        <v>0.66869185274321663</v>
       </c>
       <c r="D101">
         <f t="shared" si="4"/>
-        <v>1.1449682462139716</v>
+        <v>0.54436050780295864</v>
       </c>
       <c r="E101">
         <f t="shared" si="4"/>
-        <v>4.8627536412299268E-3</v>
+        <v>0.22559669877380806</v>
       </c>
       <c r="F101">
         <f t="shared" si="4"/>
-        <v>2.1026779706634368E-2</v>
+        <v>0.18130015938299016</v>
       </c>
       <c r="G101" t="e">
         <f t="shared" si="4"/>
@@ -22413,23 +25583,23 @@
       </c>
       <c r="B102">
         <f t="shared" si="4"/>
-        <v>0.45669547720950737</v>
+        <v>0.59752187717478389</v>
       </c>
       <c r="C102">
         <f t="shared" si="4"/>
-        <v>0.22249811989088694</v>
+        <v>0.52743261690792886</v>
       </c>
       <c r="D102">
         <f t="shared" si="4"/>
-        <v>0.79256887423517097</v>
+        <v>0.37681673380385505</v>
       </c>
       <c r="E102">
         <f t="shared" si="4"/>
-        <v>2.6459730407098828E-3</v>
+        <v>0.12275406633136897</v>
       </c>
       <c r="F102">
         <f t="shared" si="4"/>
-        <v>1.3706140350877194E-2</v>
+        <v>0.11817907757675437</v>
       </c>
       <c r="G102" t="e">
         <f t="shared" si="4"/>
@@ -22442,23 +25612,23 @@
       </c>
       <c r="B103">
         <f t="shared" si="4"/>
-        <v>0.42715999431364615</v>
+        <v>0.55887884683204481</v>
       </c>
       <c r="C103">
         <f t="shared" si="4"/>
-        <v>0.22300057682815874</v>
+        <v>0.52862369293786915</v>
       </c>
       <c r="D103">
         <f t="shared" si="4"/>
-        <v>0.61567256070531451</v>
+        <v>0.29271364415049506</v>
       </c>
       <c r="E103">
         <f t="shared" si="4"/>
-        <v>1.8473197607055873E-3</v>
+        <v>8.5702314026625037E-2</v>
       </c>
       <c r="F103">
         <f t="shared" si="4"/>
-        <v>9.2259093056211629E-3</v>
+        <v>7.9548977584730757E-2</v>
       </c>
       <c r="G103" t="e">
         <f t="shared" si="4"/>
@@ -22471,23 +25641,23 @@
       </c>
       <c r="B104">
         <f t="shared" si="4"/>
-        <v>0.3640264941394647</v>
+        <v>0.47627753059569883</v>
       </c>
       <c r="C104">
         <f t="shared" si="4"/>
-        <v>0.16484512800224188</v>
+        <v>0.39076598619971536</v>
       </c>
       <c r="D104">
         <f t="shared" si="4"/>
-        <v>0.41732743510558379</v>
+        <v>0.19841299114222519</v>
       </c>
       <c r="E104">
         <f t="shared" si="4"/>
-        <v>1.3917032220712999E-3</v>
+        <v>6.4564992540470739E-2</v>
       </c>
       <c r="F104">
         <f t="shared" si="4"/>
-        <v>7.0327444581973668E-3</v>
+        <v>6.0638752531788E-2</v>
       </c>
       <c r="G104" t="e">
         <f t="shared" si="4"/>
@@ -22500,23 +25670,23 @@
       </c>
       <c r="B105">
         <f t="shared" si="4"/>
-        <v>0.31446654800460155</v>
+        <v>0.41143530306122367</v>
       </c>
       <c r="C105">
         <f t="shared" si="4"/>
-        <v>0.12062318763660575</v>
+        <v>0.28593771284966651</v>
       </c>
       <c r="D105">
         <f t="shared" si="4"/>
-        <v>0.34221729429318443</v>
+        <v>0.16270283539861471</v>
       </c>
       <c r="E105">
         <f t="shared" si="4"/>
-        <v>8.6078194809415985E-4</v>
+        <v>3.9934074432159364E-2</v>
       </c>
       <c r="F105">
         <f t="shared" si="4"/>
-        <v>5.2689259821278034E-3</v>
+        <v>4.5430500231832739E-2</v>
       </c>
       <c r="G105" t="e">
         <f t="shared" si="4"/>
@@ -22529,23 +25699,23 @@
       </c>
       <c r="B106">
         <f t="shared" si="4"/>
-        <v>0.23976219273228239</v>
+        <v>0.31369514835640527</v>
       </c>
       <c r="C106">
         <f t="shared" si="4"/>
-        <v>0.10867021704340216</v>
+        <v>0.25760315180758414</v>
       </c>
       <c r="D106">
         <f t="shared" si="4"/>
-        <v>0.2655403037072967</v>
+        <v>0.1262477409711871</v>
       </c>
       <c r="E106">
         <f t="shared" si="4"/>
-        <v>6.8930529055596609E-4</v>
+        <v>3.1978794212041341E-2</v>
       </c>
       <c r="F106">
         <f t="shared" si="4"/>
-        <v>4.4109136590116732E-3</v>
+        <v>3.8032421538667829E-2</v>
       </c>
       <c r="G106" t="e">
         <f t="shared" si="4"/>
@@ -22558,23 +25728,23 @@
       </c>
       <c r="B107">
         <f t="shared" si="4"/>
-        <v>0.22306132937414344</v>
+        <v>0.29184441472276151</v>
       </c>
       <c r="C107">
         <f t="shared" si="4"/>
-        <v>9.4999240006079955E-2</v>
+        <v>0.22519605012951563</v>
       </c>
       <c r="D107">
         <f t="shared" si="4"/>
-        <v>0.22171506952984582</v>
+        <v>0.105411593933654</v>
       </c>
       <c r="E107">
         <f t="shared" si="4"/>
-        <v>5.2163317086198837E-4</v>
+        <v>2.4200017109568005E-2</v>
       </c>
       <c r="F107">
         <f>F97/$A107</f>
-        <v>3.6209213941416391E-3</v>
+        <v>3.1220835288630885E-2</v>
       </c>
       <c r="G107" t="e">
         <f t="shared" si="4"/>

--- a/rapport/empty-queue-data.xlsx
+++ b/rapport/empty-queue-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/baptistedupertuis/Documents/Etudes/MSE/PCM/Projet/v2/PCM_FinalProject/rapport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{316710C3-481A-AF44-B6E5-F2FBBC46F5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{48A0D006-2BDE-8247-B6DA-E0507D9B4414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35100" yWindow="-1920" windowWidth="34560" windowHeight="21100" xr2:uid="{484D20E6-2301-4D49-A5A3-FE8C8485E710}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{484D20E6-2301-4D49-A5A3-FE8C8485E710}"/>
   </bookViews>
   <sheets>
     <sheet name="empty-queue-data" sheetId="1" r:id="rId1"/>
@@ -1636,7 +1636,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="fr-FR" baseline="0%"/>
-              <a:t> villes) - Variance du temps d'exécution </a:t>
+              <a:t> villes) - écart type du temps d'exécution </a:t>
             </a:r>
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
@@ -2015,7 +2015,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -2028,14 +2028,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR"/>
+                  <a:rPr lang="fr-FR" sz="1200"/>
                   <a:t>Nombres</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="fr-FR" baseline="0%"/>
+                  <a:rPr lang="fr-FR" sz="1200" baseline="0%"/>
                   <a:t> de threads</a:t>
                 </a:r>
-                <a:endParaRPr lang="fr-FR"/>
+                <a:endParaRPr lang="fr-FR" sz="1200"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2060,7 +2060,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -2145,7 +2145,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -2158,7 +2158,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:rPr lang="fr-FR" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000">
                         <a:lumMod val="65%"/>
@@ -2166,7 +2166,7 @@
                       </a:sysClr>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>Variance du temps d'exécution [ms]</a:t>
+                  <a:t>écart type du temps d'exécution [ms]</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2184,7 +2184,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -2264,7 +2264,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65%"/>
@@ -6029,11 +6029,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="fr-FR"/>
-              <a:t>Variance</a:t>
+              <a:t>écart type du temps</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="fr-FR" baseline="0%"/>
-              <a:t> Thread execution time </a:t>
+              <a:t> d'exécution des Threads</a:t>
             </a:r>
             <a:endParaRPr lang="fr-FR"/>
           </a:p>
@@ -6043,8 +6043,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.3457673412146568"/>
-          <c:y val="2.6309292087728895E-2"/>
+          <c:x val="0.19555719020077436"/>
+          <c:y val="3.37580361264243E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -6078,7 +6078,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10705302167830111"/>
+          <c:y val="0.13813926099015986"/>
+          <c:w val="0.61502670058319275"/>
+          <c:h val="0.71374644639131657"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -6697,7 +6707,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -6710,7 +6720,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR"/>
+                  <a:rPr lang="fr-FR" sz="1200"/>
                   <a:t>Nombre de villes</a:t>
                 </a:r>
               </a:p>
@@ -6720,8 +6730,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.38351469442618502"/>
-              <c:y val="0.92672953671488745"/>
+              <c:x val="0.3272647129585437"/>
+              <c:y val="0.91928066221024929"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -6737,7 +6747,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -6825,7 +6835,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -6838,14 +6848,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR"/>
-                  <a:t>Variance du temps d'exécution</a:t>
+                  <a:rPr lang="fr-FR" sz="1200"/>
+                  <a:t>écart type du temps d'exécution</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="fr-FR" baseline="0%"/>
+                  <a:rPr lang="fr-FR" sz="1200" baseline="0%"/>
                   <a:t> [ms]</a:t>
                 </a:r>
-                <a:endParaRPr lang="fr-FR"/>
+                <a:endParaRPr lang="fr-FR" sz="1200"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -6862,7 +6872,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -6942,7 +6952,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65%"/>
@@ -11672,7 +11682,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -11685,14 +11695,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR"/>
+                  <a:rPr lang="fr-FR" sz="1200"/>
                   <a:t>Nombres</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="fr-FR" baseline="0%"/>
+                  <a:rPr lang="fr-FR" sz="1200" baseline="0%"/>
                   <a:t> de threads</a:t>
                 </a:r>
-                <a:endParaRPr lang="fr-FR"/>
+                <a:endParaRPr lang="fr-FR" sz="1200"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -11717,7 +11727,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -11802,7 +11812,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65%"/>
@@ -11815,14 +11825,14 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="fr-FR"/>
+                  <a:rPr lang="fr-FR" sz="1200"/>
                   <a:t>Temps d'exécution</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="fr-FR" baseline="0%"/>
+                  <a:rPr lang="fr-FR" sz="1200" baseline="0%"/>
                   <a:t> [ms]</a:t>
                 </a:r>
-                <a:endParaRPr lang="fr-FR"/>
+                <a:endParaRPr lang="fr-FR" sz="1200"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -11839,7 +11849,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65%"/>
@@ -11919,7 +11929,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0%">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65%"/>
@@ -20289,16 +20299,16 @@
 <xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>14596</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>32799</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>620890</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>173910</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>818288</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>14598</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>156479</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>25486</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -20361,14 +20371,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>10162</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>172720</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>649109</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>19650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>465666</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>71120</xdr:rowOff>
     </xdr:to>
@@ -20403,10 +20413,10 @@
       <xdr:rowOff>175173</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>72989</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>441759</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>42333</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -20590,8 +20600,8 @@
 <xdr:wsDr xmlns:xdr="http://purl.oclc.org/ooxml/drawingml/spreadsheetDrawing" xmlns:a="http://purl.oclc.org/ooxml/drawingml/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>774700</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
@@ -20599,7 +20609,7 @@
       <xdr:col>16</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>177800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -20626,16 +20636,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:colOff>203200</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22517,6 +22527,10 @@
       <c r="D66">
         <v>0.59199999999999997</v>
       </c>
+      <c r="E66">
+        <f>C66/1000/60</f>
+        <v>3.6464583333333334</v>
+      </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67">
@@ -22531,6 +22545,10 @@
       <c r="D67">
         <v>2.0594000000000001</v>
       </c>
+      <c r="E67">
+        <f t="shared" ref="E67:E73" si="1">C67/1000/60</f>
+        <v>1.8529783333333332</v>
+      </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68">
@@ -22545,6 +22563,10 @@
       <c r="D68">
         <v>2.2751000000000001</v>
       </c>
+      <c r="E68">
+        <f t="shared" si="1"/>
+        <v>1.7943316666666667</v>
+      </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69">
@@ -22559,6 +22581,10 @@
       <c r="D69">
         <v>2.8868999999999998</v>
       </c>
+      <c r="E69">
+        <f t="shared" si="1"/>
+        <v>1.30114</v>
+      </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70">
@@ -22573,6 +22599,10 @@
       <c r="D70">
         <v>3.6686999999999999</v>
       </c>
+      <c r="E70">
+        <f t="shared" si="1"/>
+        <v>1.3090316666666666</v>
+      </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71">
@@ -22587,6 +22617,10 @@
       <c r="D71">
         <v>11.0329</v>
       </c>
+      <c r="E71">
+        <f t="shared" si="1"/>
+        <v>1.3107800000000001</v>
+      </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72">
@@ -22601,6 +22635,10 @@
       <c r="D72">
         <v>5.6379000000000001</v>
       </c>
+      <c r="E72">
+        <f t="shared" si="1"/>
+        <v>1.2412416666666668</v>
+      </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73">
@@ -22614,6 +22652,10 @@
       </c>
       <c r="D73">
         <v>6.9047999999999998</v>
+      </c>
+      <c r="E73">
+        <f t="shared" si="1"/>
+        <v>1.2880833333333332</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="13" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -22927,7 +22969,7 @@
         <v>29.90023479403531</v>
       </c>
       <c r="C90">
-        <f t="shared" ref="C90:G90" si="1">C$87/C77</f>
+        <f t="shared" ref="C90:G90" si="2">C$87/C77</f>
         <v>26.351678867785573</v>
       </c>
       <c r="D90">
@@ -22935,15 +22977,15 @@
         <v>24.889014243491729</v>
       </c>
       <c r="E90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.783993820007726</v>
       </c>
       <c r="F90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10.877186199066481</v>
       </c>
       <c r="G90">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.204987318422873</v>
       </c>
     </row>
@@ -22952,27 +22994,27 @@
         <v>64</v>
       </c>
       <c r="B91">
-        <f t="shared" ref="B91:C97" si="2">B$87/B78</f>
+        <f t="shared" ref="B91:C97" si="3">B$87/B78</f>
         <v>58.840385973212499</v>
       </c>
       <c r="C91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>53.626250212084081</v>
       </c>
       <c r="D91">
-        <f t="shared" ref="D91:G97" si="3">D$87/D78</f>
+        <f t="shared" ref="D91:G97" si="4">D$87/D78</f>
         <v>39.267316017688458</v>
       </c>
       <c r="E91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.015737908654678</v>
       </c>
       <c r="F91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12.576349912485414</v>
       </c>
       <c r="G91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.916053154495776</v>
       </c>
     </row>
@@ -22981,27 +23023,27 @@
         <v>96</v>
       </c>
       <c r="B92">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>60.763549102312005</v>
       </c>
       <c r="C92">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>63.065578310849006</v>
       </c>
       <c r="D92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>45.712369148488676</v>
       </c>
       <c r="E92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.608594851967208</v>
       </c>
       <c r="F92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>12.120249508012369</v>
       </c>
       <c r="G92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9.4022680169571355</v>
       </c>
     </row>
@@ -23010,27 +23052,27 @@
         <v>128</v>
       </c>
       <c r="B93">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>83.795717857673537</v>
       </c>
       <c r="C93">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>74.113463885831152</v>
       </c>
       <c r="D93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>48.582164708136425</v>
       </c>
       <c r="E93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.675456669422381</v>
       </c>
       <c r="F93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10.545921599804304</v>
       </c>
       <c r="G93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.3327134209977043</v>
       </c>
     </row>
@@ -23039,27 +23081,27 @@
         <v>160</v>
       </c>
       <c r="B94">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>83.290544537374331</v>
       </c>
       <c r="C94">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>68.630266476871768</v>
       </c>
       <c r="D94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>49.876485739263472</v>
       </c>
       <c r="E94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.709089861336214</v>
       </c>
       <c r="F94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10.025983139534883</v>
       </c>
       <c r="G94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.8726148688621569</v>
       </c>
     </row>
@@ -23068,27 +23110,27 @@
         <v>192</v>
       </c>
       <c r="B95">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>83.179450657878007</v>
       </c>
       <c r="C95">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>70.722600629009008</v>
       </c>
       <c r="D95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>52.569593075487781</v>
       </c>
       <c r="E95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.618113694164848</v>
       </c>
       <c r="F95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.9313709343277399</v>
       </c>
       <c r="G95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.0658460176991147</v>
       </c>
     </row>
@@ -23097,27 +23139,27 @@
         <v>224</v>
       </c>
       <c r="B96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>87.8394298719696</v>
       </c>
       <c r="C96">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>69.667763280350712</v>
       </c>
       <c r="D96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>54.294313975066622</v>
       </c>
       <c r="E96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.503428551100992</v>
       </c>
       <c r="F96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8.4723842979266966</v>
       </c>
       <c r="G96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.6759247491638796</v>
       </c>
     </row>
@@ -23126,27 +23168,27 @@
         <v>256</v>
       </c>
       <c r="B97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>84.645113799573011</v>
       </c>
       <c r="C97">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>72.932497740572899</v>
       </c>
       <c r="D97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>54.682000407341739</v>
       </c>
       <c r="E97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.598493023255813</v>
       </c>
       <c r="F97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7.8249800344858871</v>
       </c>
       <c r="G97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.12865059871047</v>
       </c>
     </row>
@@ -23182,19 +23224,19 @@
         <v>0.93438233731360343</v>
       </c>
       <c r="C100">
-        <f t="shared" ref="C100:F100" si="4">C90/$A100</f>
+        <f t="shared" ref="C100:F100" si="5">C90/$A100</f>
         <v>0.82348996461829915</v>
       </c>
       <c r="D100">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.77778169510911654</v>
       </c>
       <c r="E100">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.43074980687524145</v>
       </c>
       <c r="F100">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.33991206872082752</v>
       </c>
       <c r="G100">
@@ -23207,27 +23249,27 @@
         <v>64</v>
       </c>
       <c r="B101">
-        <f t="shared" ref="B101:G107" si="5">B91/$A101</f>
+        <f t="shared" ref="B101:G107" si="6">B91/$A101</f>
         <v>0.91938103083144529</v>
       </c>
       <c r="C101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.83791015956381376</v>
       </c>
       <c r="D101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.61355181277638215</v>
       </c>
       <c r="E101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25024590482272935</v>
       </c>
       <c r="F101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.19650546738258459</v>
       </c>
       <c r="G101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.1549383305389965</v>
       </c>
     </row>
@@ -23236,27 +23278,27 @@
         <v>96</v>
       </c>
       <c r="B102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.63295363648241676</v>
       </c>
       <c r="C102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.65693310740467714</v>
       </c>
       <c r="D102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.47617051196342369</v>
       </c>
       <c r="E102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.17300619637465842</v>
       </c>
       <c r="F102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.1262525990417955</v>
       </c>
       <c r="G102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.7940291843303495E-2</v>
       </c>
     </row>
@@ -23265,27 +23307,27 @@
         <v>128</v>
       </c>
       <c r="B103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.65465404576307451</v>
       </c>
       <c r="C103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.57901143660805587</v>
       </c>
       <c r="D103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.37954816178231582</v>
       </c>
       <c r="E103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.13027700522986235</v>
       </c>
       <c r="F103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.2390012498471124E-2</v>
       </c>
       <c r="G103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.5099323601544565E-2</v>
       </c>
     </row>
@@ -23294,27 +23336,27 @@
         <v>160</v>
       </c>
       <c r="B104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.52056590335858954</v>
       </c>
       <c r="C104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.42893916548044853</v>
       </c>
       <c r="D104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.31172803587039671</v>
       </c>
       <c r="E104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.10443181163335133</v>
       </c>
       <c r="F104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.2662394622093026E-2</v>
       </c>
       <c r="G104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.9203842930388479E-2</v>
       </c>
     </row>
@@ -23323,27 +23365,27 @@
         <v>192</v>
       </c>
       <c r="B105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.43322630550978131</v>
       </c>
       <c r="C105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.36834687827608859</v>
       </c>
       <c r="D105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.27379996393483219</v>
       </c>
       <c r="E105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.6552675490441919E-2</v>
       </c>
       <c r="F105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4.6517556949623645E-2</v>
       </c>
       <c r="G105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.6801281342182891E-2</v>
       </c>
     </row>
@@ -23352,27 +23394,27 @@
         <v>224</v>
       </c>
       <c r="B106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.39214031192843574</v>
       </c>
       <c r="C106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.31101680035870855</v>
       </c>
       <c r="D106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.24238533024583314</v>
       </c>
       <c r="E106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7.3676020317415145E-2</v>
       </c>
       <c r="F106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.7823144187172753E-2</v>
       </c>
       <c r="G106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.9803235487338747E-2</v>
       </c>
     </row>
@@ -23381,27 +23423,27 @@
         <v>256</v>
       </c>
       <c r="B107">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.33064497577958207</v>
       </c>
       <c r="C107">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.28489256929911289</v>
       </c>
       <c r="D107">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.21360156409117867</v>
       </c>
       <c r="E107">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6.4837863372093019E-2</v>
       </c>
       <c r="F107">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.0566328259710496E-2</v>
       </c>
       <c r="G107">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.3940041401212774E-2</v>
       </c>
     </row>
